--- a/artfynd/A 31799-2020 artfynd.xlsx
+++ b/artfynd/A 31799-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121476957</v>
       </c>
       <c r="B2" t="n">
-        <v>90727</v>
+        <v>90728</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121476799</v>
+        <v>121476482</v>
       </c>
       <c r="B4" t="n">
-        <v>90705</v>
+        <v>56563</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585517</v>
+        <v>585919</v>
       </c>
       <c r="R4" t="n">
-        <v>7268168</v>
+        <v>7268414</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121476802</v>
+        <v>121476691</v>
       </c>
       <c r="B5" t="n">
-        <v>90705</v>
+        <v>91065</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>1506</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585846</v>
+        <v>585866</v>
       </c>
       <c r="R5" t="n">
-        <v>7268570</v>
+        <v>7268608</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121476645</v>
+        <v>121476725</v>
       </c>
       <c r="B6" t="n">
-        <v>90995</v>
+        <v>77945</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585866</v>
+        <v>585865</v>
       </c>
       <c r="R6" t="n">
-        <v>7268608</v>
+        <v>7268520</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,7 +1188,7 @@
         <v>121476857</v>
       </c>
       <c r="B7" t="n">
-        <v>90723</v>
+        <v>90724</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121477106</v>
+        <v>121476801</v>
       </c>
       <c r="B8" t="n">
-        <v>78604</v>
+        <v>90706</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121476482</v>
+        <v>121476959</v>
       </c>
       <c r="B9" t="n">
-        <v>56563</v>
+        <v>90728</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585919</v>
+        <v>585881</v>
       </c>
       <c r="R9" t="n">
-        <v>7268414</v>
+        <v>7268466</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121476691</v>
+        <v>121476960</v>
       </c>
       <c r="B10" t="n">
-        <v>91064</v>
+        <v>90728</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1506</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585866</v>
+        <v>585838</v>
       </c>
       <c r="R10" t="n">
-        <v>7268608</v>
+        <v>7268532</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121476959</v>
+        <v>121477106</v>
       </c>
       <c r="B11" t="n">
-        <v>90727</v>
+        <v>78604</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585881</v>
+        <v>585865</v>
       </c>
       <c r="R11" t="n">
-        <v>7268466</v>
+        <v>7268520</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121476725</v>
+        <v>121477108</v>
       </c>
       <c r="B12" t="n">
-        <v>77945</v>
+        <v>78604</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>498</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585865</v>
+        <v>585846</v>
       </c>
       <c r="R12" t="n">
-        <v>7268520</v>
+        <v>7268570</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121477108</v>
+        <v>121476645</v>
       </c>
       <c r="B13" t="n">
-        <v>78604</v>
+        <v>90996</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585846</v>
+        <v>585866</v>
       </c>
       <c r="R13" t="n">
-        <v>7268570</v>
+        <v>7268608</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121476801</v>
+        <v>121476956</v>
       </c>
       <c r="B14" t="n">
-        <v>90705</v>
+        <v>90728</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585865</v>
+        <v>585827</v>
       </c>
       <c r="R14" t="n">
-        <v>7268520</v>
+        <v>7268201</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2004,7 +2004,7 @@
         <v>121476384</v>
       </c>
       <c r="B15" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121476956</v>
+        <v>121476802</v>
       </c>
       <c r="B16" t="n">
-        <v>90727</v>
+        <v>90706</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585827</v>
+        <v>585846</v>
       </c>
       <c r="R16" t="n">
-        <v>7268201</v>
+        <v>7268570</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121476960</v>
+        <v>121476799</v>
       </c>
       <c r="B17" t="n">
-        <v>90727</v>
+        <v>90706</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585838</v>
+        <v>585517</v>
       </c>
       <c r="R17" t="n">
-        <v>7268532</v>
+        <v>7268168</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 31799-2020 artfynd.xlsx
+++ b/artfynd/A 31799-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121476957</v>
+        <v>121477102</v>
       </c>
       <c r="B2" t="n">
-        <v>90728</v>
+        <v>78607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585911</v>
+        <v>585517</v>
       </c>
       <c r="R2" t="n">
-        <v>7268305</v>
+        <v>7268168</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121477102</v>
+        <v>121476799</v>
       </c>
       <c r="B3" t="n">
-        <v>78604</v>
+        <v>90709</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121476482</v>
+        <v>121477108</v>
       </c>
       <c r="B4" t="n">
-        <v>56563</v>
+        <v>78607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585919</v>
+        <v>585846</v>
       </c>
       <c r="R4" t="n">
-        <v>7268414</v>
+        <v>7268570</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121476691</v>
+        <v>121476482</v>
       </c>
       <c r="B5" t="n">
-        <v>91065</v>
+        <v>56566</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1506</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585866</v>
+        <v>585919</v>
       </c>
       <c r="R5" t="n">
-        <v>7268608</v>
+        <v>7268414</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121476725</v>
+        <v>121476802</v>
       </c>
       <c r="B6" t="n">
-        <v>77945</v>
+        <v>90709</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>498</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585865</v>
+        <v>585846</v>
       </c>
       <c r="R6" t="n">
-        <v>7268520</v>
+        <v>7268570</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121476857</v>
+        <v>121476801</v>
       </c>
       <c r="B7" t="n">
-        <v>90724</v>
+        <v>90709</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585596</v>
+        <v>585865</v>
       </c>
       <c r="R7" t="n">
-        <v>7268207</v>
+        <v>7268520</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121476801</v>
+        <v>121476691</v>
       </c>
       <c r="B8" t="n">
-        <v>90706</v>
+        <v>91068</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>1506</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585865</v>
+        <v>585866</v>
       </c>
       <c r="R8" t="n">
-        <v>7268520</v>
+        <v>7268608</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121476959</v>
+        <v>121476857</v>
       </c>
       <c r="B9" t="n">
-        <v>90728</v>
+        <v>90727</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585881</v>
+        <v>585596</v>
       </c>
       <c r="R9" t="n">
-        <v>7268466</v>
+        <v>7268207</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121476960</v>
+        <v>121476645</v>
       </c>
       <c r="B10" t="n">
-        <v>90728</v>
+        <v>90999</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585838</v>
+        <v>585866</v>
       </c>
       <c r="R10" t="n">
-        <v>7268532</v>
+        <v>7268608</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121477106</v>
+        <v>121476725</v>
       </c>
       <c r="B11" t="n">
-        <v>78604</v>
+        <v>77948</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121477108</v>
+        <v>121477106</v>
       </c>
       <c r="B12" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585846</v>
+        <v>585865</v>
       </c>
       <c r="R12" t="n">
-        <v>7268570</v>
+        <v>7268520</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121476645</v>
+        <v>121476957</v>
       </c>
       <c r="B13" t="n">
-        <v>90996</v>
+        <v>90731</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585866</v>
+        <v>585911</v>
       </c>
       <c r="R13" t="n">
-        <v>7268608</v>
+        <v>7268305</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121476956</v>
+        <v>121476384</v>
       </c>
       <c r="B14" t="n">
-        <v>90728</v>
+        <v>90713</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585827</v>
+        <v>585866</v>
       </c>
       <c r="R14" t="n">
-        <v>7268201</v>
+        <v>7268608</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121476384</v>
+        <v>121476960</v>
       </c>
       <c r="B15" t="n">
-        <v>90710</v>
+        <v>90731</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585866</v>
+        <v>585838</v>
       </c>
       <c r="R15" t="n">
-        <v>7268608</v>
+        <v>7268532</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121476802</v>
+        <v>121476956</v>
       </c>
       <c r="B16" t="n">
-        <v>90706</v>
+        <v>90731</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585846</v>
+        <v>585827</v>
       </c>
       <c r="R16" t="n">
-        <v>7268570</v>
+        <v>7268201</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121476799</v>
+        <v>121476959</v>
       </c>
       <c r="B17" t="n">
-        <v>90706</v>
+        <v>90731</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585517</v>
+        <v>585881</v>
       </c>
       <c r="R17" t="n">
-        <v>7268168</v>
+        <v>7268466</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 31799-2020 artfynd.xlsx
+++ b/artfynd/A 31799-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121477102</v>
+        <v>121476725</v>
       </c>
       <c r="B2" t="n">
-        <v>78607</v>
+        <v>77948</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585517</v>
+        <v>585865</v>
       </c>
       <c r="R2" t="n">
-        <v>7268168</v>
+        <v>7268520</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121476799</v>
+        <v>121477102</v>
       </c>
       <c r="B3" t="n">
-        <v>90709</v>
+        <v>78607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121476482</v>
+        <v>121476802</v>
       </c>
       <c r="B5" t="n">
-        <v>56566</v>
+        <v>90709</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585919</v>
+        <v>585846</v>
       </c>
       <c r="R5" t="n">
-        <v>7268414</v>
+        <v>7268570</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121476802</v>
+        <v>121476691</v>
       </c>
       <c r="B6" t="n">
-        <v>90709</v>
+        <v>91068</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>1506</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585846</v>
+        <v>585866</v>
       </c>
       <c r="R6" t="n">
-        <v>7268570</v>
+        <v>7268608</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121476691</v>
+        <v>121476857</v>
       </c>
       <c r="B8" t="n">
-        <v>91068</v>
+        <v>90727</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1506</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585866</v>
+        <v>585596</v>
       </c>
       <c r="R8" t="n">
-        <v>7268608</v>
+        <v>7268207</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121476857</v>
+        <v>121476960</v>
       </c>
       <c r="B9" t="n">
-        <v>90727</v>
+        <v>90731</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585596</v>
+        <v>585838</v>
       </c>
       <c r="R9" t="n">
-        <v>7268207</v>
+        <v>7268532</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121476645</v>
+        <v>121477106</v>
       </c>
       <c r="B10" t="n">
-        <v>90999</v>
+        <v>78607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585866</v>
+        <v>585865</v>
       </c>
       <c r="R10" t="n">
-        <v>7268608</v>
+        <v>7268520</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121476725</v>
+        <v>121476959</v>
       </c>
       <c r="B11" t="n">
-        <v>77948</v>
+        <v>90731</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>498</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585865</v>
+        <v>585881</v>
       </c>
       <c r="R11" t="n">
-        <v>7268520</v>
+        <v>7268466</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121477106</v>
+        <v>121476482</v>
       </c>
       <c r="B12" t="n">
-        <v>78607</v>
+        <v>56566</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585865</v>
+        <v>585919</v>
       </c>
       <c r="R12" t="n">
-        <v>7268520</v>
+        <v>7268414</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121476384</v>
+        <v>121476645</v>
       </c>
       <c r="B14" t="n">
-        <v>90713</v>
+        <v>90999</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121476960</v>
+        <v>121476956</v>
       </c>
       <c r="B15" t="n">
         <v>90731</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585838</v>
+        <v>585827</v>
       </c>
       <c r="R15" t="n">
-        <v>7268532</v>
+        <v>7268201</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121476956</v>
+        <v>121476384</v>
       </c>
       <c r="B16" t="n">
-        <v>90731</v>
+        <v>90713</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585827</v>
+        <v>585866</v>
       </c>
       <c r="R16" t="n">
-        <v>7268201</v>
+        <v>7268608</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121476959</v>
+        <v>121476799</v>
       </c>
       <c r="B17" t="n">
-        <v>90731</v>
+        <v>90709</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585881</v>
+        <v>585517</v>
       </c>
       <c r="R17" t="n">
-        <v>7268466</v>
+        <v>7268168</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2304,6 +2304,1746 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121532894</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78607</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>585864</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7268519</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121532587</v>
+      </c>
+      <c r="B19" t="n">
+        <v>90709</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>585864</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7268519</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121532260</v>
+      </c>
+      <c r="B20" t="n">
+        <v>90713</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>585865</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7268608</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121532585</v>
+      </c>
+      <c r="B21" t="n">
+        <v>90709</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>585516</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7268167</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121532739</v>
+      </c>
+      <c r="B22" t="n">
+        <v>90731</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>585910</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7268305</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121532165</v>
+      </c>
+      <c r="B23" t="n">
+        <v>77948</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>498</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Liten sotlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Acolium karelicum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>585864</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7268519</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121532149</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91068</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1506</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ostticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Skeletocutis odora</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>585865</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7268608</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>121532890</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78607</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>585516</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7268167</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>121532738</v>
+      </c>
+      <c r="B26" t="n">
+        <v>90731</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>585826</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7268200</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>121532588</v>
+      </c>
+      <c r="B27" t="n">
+        <v>90709</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>585845</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7268570</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>121532741</v>
+      </c>
+      <c r="B28" t="n">
+        <v>90731</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>585880</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7268465</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>121532896</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78607</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>585845</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7268570</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>121532743</v>
+      </c>
+      <c r="B30" t="n">
+        <v>90731</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>585837</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7268531</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>121532473</v>
+      </c>
+      <c r="B31" t="n">
+        <v>90999</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>658</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>585865</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7268608</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>121532642</v>
+      </c>
+      <c r="B32" t="n">
+        <v>90727</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>585595</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7268207</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31799-2020 artfynd.xlsx
+++ b/artfynd/A 31799-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121476725</v>
+        <v>121476956</v>
       </c>
       <c r="B2" t="n">
-        <v>77948</v>
+        <v>90737</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>498</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585865</v>
+        <v>585827</v>
       </c>
       <c r="R2" t="n">
-        <v>7268520</v>
+        <v>7268201</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121477102</v>
+        <v>121477108</v>
       </c>
       <c r="B3" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585517</v>
+        <v>585846</v>
       </c>
       <c r="R3" t="n">
-        <v>7268168</v>
+        <v>7268570</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121477108</v>
+        <v>121476802</v>
       </c>
       <c r="B4" t="n">
-        <v>78607</v>
+        <v>90715</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121476802</v>
+        <v>121476957</v>
       </c>
       <c r="B5" t="n">
-        <v>90709</v>
+        <v>90737</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585846</v>
+        <v>585911</v>
       </c>
       <c r="R5" t="n">
-        <v>7268570</v>
+        <v>7268305</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121476691</v>
+        <v>121476857</v>
       </c>
       <c r="B6" t="n">
-        <v>91068</v>
+        <v>90733</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1506</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585866</v>
+        <v>585596</v>
       </c>
       <c r="R6" t="n">
-        <v>7268608</v>
+        <v>7268207</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121476801</v>
+        <v>121476645</v>
       </c>
       <c r="B7" t="n">
-        <v>90709</v>
+        <v>91005</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585865</v>
+        <v>585866</v>
       </c>
       <c r="R7" t="n">
-        <v>7268520</v>
+        <v>7268608</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121476857</v>
+        <v>121476691</v>
       </c>
       <c r="B8" t="n">
-        <v>90727</v>
+        <v>91074</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>1506</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585596</v>
+        <v>585866</v>
       </c>
       <c r="R8" t="n">
-        <v>7268207</v>
+        <v>7268608</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
         <v>121476960</v>
       </c>
       <c r="B9" t="n">
-        <v>90731</v>
+        <v>90737</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121477106</v>
+        <v>121476799</v>
       </c>
       <c r="B10" t="n">
-        <v>78607</v>
+        <v>90715</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585865</v>
+        <v>585517</v>
       </c>
       <c r="R10" t="n">
-        <v>7268520</v>
+        <v>7268168</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121476959</v>
+        <v>121477106</v>
       </c>
       <c r="B11" t="n">
-        <v>90731</v>
+        <v>78608</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585881</v>
+        <v>585865</v>
       </c>
       <c r="R11" t="n">
-        <v>7268466</v>
+        <v>7268520</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,7 +1698,7 @@
         <v>121476482</v>
       </c>
       <c r="B12" t="n">
-        <v>56566</v>
+        <v>56567</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121476957</v>
+        <v>121476384</v>
       </c>
       <c r="B13" t="n">
-        <v>90731</v>
+        <v>90719</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585911</v>
+        <v>585866</v>
       </c>
       <c r="R13" t="n">
-        <v>7268305</v>
+        <v>7268608</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121476645</v>
+        <v>121476725</v>
       </c>
       <c r="B14" t="n">
-        <v>90999</v>
+        <v>77949</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585866</v>
+        <v>585865</v>
       </c>
       <c r="R14" t="n">
-        <v>7268608</v>
+        <v>7268520</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121476956</v>
+        <v>121476801</v>
       </c>
       <c r="B15" t="n">
-        <v>90731</v>
+        <v>90715</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585827</v>
+        <v>585865</v>
       </c>
       <c r="R15" t="n">
-        <v>7268201</v>
+        <v>7268520</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121476384</v>
+        <v>121476959</v>
       </c>
       <c r="B16" t="n">
-        <v>90713</v>
+        <v>90737</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585866</v>
+        <v>585881</v>
       </c>
       <c r="R16" t="n">
-        <v>7268608</v>
+        <v>7268466</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121476799</v>
+        <v>121477102</v>
       </c>
       <c r="B17" t="n">
-        <v>90709</v>
+        <v>78608</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121532894</v>
+        <v>121532739</v>
       </c>
       <c r="B18" t="n">
-        <v>78607</v>
+        <v>90737</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585864</v>
+        <v>585910</v>
       </c>
       <c r="R18" t="n">
-        <v>7268519</v>
+        <v>7268305</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2423,10 +2423,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121532587</v>
+        <v>121532642</v>
       </c>
       <c r="B19" t="n">
-        <v>90709</v>
+        <v>90733</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2439,21 +2439,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2467,10 +2467,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585864</v>
+        <v>585595</v>
       </c>
       <c r="R19" t="n">
-        <v>7268519</v>
+        <v>7268207</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2539,10 +2539,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121532260</v>
+        <v>121532587</v>
       </c>
       <c r="B20" t="n">
-        <v>90713</v>
+        <v>90715</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2555,21 +2555,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585865</v>
+        <v>585864</v>
       </c>
       <c r="R20" t="n">
-        <v>7268608</v>
+        <v>7268519</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2655,10 +2655,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121532585</v>
+        <v>121532890</v>
       </c>
       <c r="B21" t="n">
-        <v>90709</v>
+        <v>78608</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2671,21 +2671,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2771,10 +2771,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121532739</v>
+        <v>121532738</v>
       </c>
       <c r="B22" t="n">
-        <v>90731</v>
+        <v>90737</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2815,10 +2815,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585910</v>
+        <v>585826</v>
       </c>
       <c r="R22" t="n">
-        <v>7268305</v>
+        <v>7268200</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2887,10 +2887,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121532165</v>
+        <v>121532260</v>
       </c>
       <c r="B23" t="n">
-        <v>77948</v>
+        <v>90719</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2899,25 +2899,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>498</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585864</v>
+        <v>585865</v>
       </c>
       <c r="R23" t="n">
-        <v>7268519</v>
+        <v>7268608</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3003,10 +3003,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121532149</v>
+        <v>121532585</v>
       </c>
       <c r="B24" t="n">
-        <v>91068</v>
+        <v>90715</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3015,25 +3015,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1506</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585865</v>
+        <v>585516</v>
       </c>
       <c r="R24" t="n">
-        <v>7268608</v>
+        <v>7268167</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3119,10 +3119,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121532890</v>
+        <v>121532894</v>
       </c>
       <c r="B25" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585516</v>
+        <v>585864</v>
       </c>
       <c r="R25" t="n">
-        <v>7268167</v>
+        <v>7268519</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3235,10 +3235,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121532738</v>
+        <v>121532473</v>
       </c>
       <c r="B26" t="n">
-        <v>90731</v>
+        <v>91005</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3251,21 +3251,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585826</v>
+        <v>585865</v>
       </c>
       <c r="R26" t="n">
-        <v>7268200</v>
+        <v>7268608</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3351,10 +3351,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121532588</v>
+        <v>121532165</v>
       </c>
       <c r="B27" t="n">
-        <v>90709</v>
+        <v>77949</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3363,25 +3363,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3395,10 +3395,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585845</v>
+        <v>585864</v>
       </c>
       <c r="R27" t="n">
-        <v>7268570</v>
+        <v>7268519</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3467,10 +3467,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121532741</v>
+        <v>121532743</v>
       </c>
       <c r="B28" t="n">
-        <v>90731</v>
+        <v>90737</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585880</v>
+        <v>585837</v>
       </c>
       <c r="R28" t="n">
-        <v>7268465</v>
+        <v>7268531</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3583,10 +3583,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121532896</v>
+        <v>121532149</v>
       </c>
       <c r="B29" t="n">
-        <v>78607</v>
+        <v>91074</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3595,25 +3595,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585845</v>
+        <v>585865</v>
       </c>
       <c r="R29" t="n">
-        <v>7268570</v>
+        <v>7268608</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3699,10 +3699,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121532743</v>
+        <v>121532588</v>
       </c>
       <c r="B30" t="n">
-        <v>90731</v>
+        <v>90715</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3715,21 +3715,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3743,10 +3743,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585837</v>
+        <v>585845</v>
       </c>
       <c r="R30" t="n">
-        <v>7268531</v>
+        <v>7268570</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3815,10 +3815,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121532473</v>
+        <v>121532741</v>
       </c>
       <c r="B31" t="n">
-        <v>90999</v>
+        <v>90737</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3831,21 +3831,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585865</v>
+        <v>585880</v>
       </c>
       <c r="R31" t="n">
-        <v>7268608</v>
+        <v>7268465</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3931,10 +3931,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121532642</v>
+        <v>121532896</v>
       </c>
       <c r="B32" t="n">
-        <v>90727</v>
+        <v>78608</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3947,21 +3947,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585595</v>
+        <v>585845</v>
       </c>
       <c r="R32" t="n">
-        <v>7268207</v>
+        <v>7268570</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 31799-2020 artfynd.xlsx
+++ b/artfynd/A 31799-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121476956</v>
+        <v>121476802</v>
       </c>
       <c r="B2" t="n">
-        <v>90737</v>
+        <v>90715</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585827</v>
+        <v>585846</v>
       </c>
       <c r="R2" t="n">
-        <v>7268201</v>
+        <v>7268570</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121477108</v>
+        <v>121476956</v>
       </c>
       <c r="B3" t="n">
-        <v>78608</v>
+        <v>90737</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585846</v>
+        <v>585827</v>
       </c>
       <c r="R3" t="n">
-        <v>7268570</v>
+        <v>7268201</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121476802</v>
+        <v>121477108</v>
       </c>
       <c r="B4" t="n">
-        <v>90715</v>
+        <v>78608</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>

--- a/artfynd/A 31799-2020 artfynd.xlsx
+++ b/artfynd/A 31799-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121476802</v>
+        <v>121476691</v>
       </c>
       <c r="B2" t="n">
-        <v>90715</v>
+        <v>91075</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>1506</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585846</v>
+        <v>585866</v>
       </c>
       <c r="R2" t="n">
-        <v>7268570</v>
+        <v>7268608</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121476956</v>
+        <v>121476482</v>
       </c>
       <c r="B3" t="n">
-        <v>90737</v>
+        <v>56568</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585827</v>
+        <v>585919</v>
       </c>
       <c r="R3" t="n">
-        <v>7268201</v>
+        <v>7268414</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121477108</v>
+        <v>121476857</v>
       </c>
       <c r="B4" t="n">
-        <v>78608</v>
+        <v>90734</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585846</v>
+        <v>585596</v>
       </c>
       <c r="R4" t="n">
-        <v>7268570</v>
+        <v>7268207</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121476957</v>
+        <v>121477108</v>
       </c>
       <c r="B5" t="n">
-        <v>90737</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585911</v>
+        <v>585846</v>
       </c>
       <c r="R5" t="n">
-        <v>7268305</v>
+        <v>7268570</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121476857</v>
+        <v>121476960</v>
       </c>
       <c r="B6" t="n">
-        <v>90733</v>
+        <v>90738</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585596</v>
+        <v>585838</v>
       </c>
       <c r="R6" t="n">
-        <v>7268207</v>
+        <v>7268532</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,7 +1188,7 @@
         <v>121476645</v>
       </c>
       <c r="B7" t="n">
-        <v>91005</v>
+        <v>91006</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121476691</v>
+        <v>121476384</v>
       </c>
       <c r="B8" t="n">
-        <v>91074</v>
+        <v>90720</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121476960</v>
+        <v>121477106</v>
       </c>
       <c r="B9" t="n">
-        <v>90737</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585838</v>
+        <v>585865</v>
       </c>
       <c r="R9" t="n">
-        <v>7268532</v>
+        <v>7268520</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121476799</v>
+        <v>121476725</v>
       </c>
       <c r="B10" t="n">
-        <v>90715</v>
+        <v>77950</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585517</v>
+        <v>585865</v>
       </c>
       <c r="R10" t="n">
-        <v>7268168</v>
+        <v>7268520</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121477106</v>
+        <v>121477102</v>
       </c>
       <c r="B11" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585865</v>
+        <v>585517</v>
       </c>
       <c r="R11" t="n">
-        <v>7268520</v>
+        <v>7268168</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121476482</v>
+        <v>121476799</v>
       </c>
       <c r="B12" t="n">
-        <v>56567</v>
+        <v>90716</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585919</v>
+        <v>585517</v>
       </c>
       <c r="R12" t="n">
-        <v>7268414</v>
+        <v>7268168</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121476384</v>
+        <v>121476956</v>
       </c>
       <c r="B13" t="n">
-        <v>90719</v>
+        <v>90738</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585866</v>
+        <v>585827</v>
       </c>
       <c r="R13" t="n">
-        <v>7268608</v>
+        <v>7268201</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121476725</v>
+        <v>121476957</v>
       </c>
       <c r="B14" t="n">
-        <v>77949</v>
+        <v>90738</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>498</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585865</v>
+        <v>585911</v>
       </c>
       <c r="R14" t="n">
-        <v>7268520</v>
+        <v>7268305</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2004,7 +2004,7 @@
         <v>121476801</v>
       </c>
       <c r="B15" t="n">
-        <v>90715</v>
+        <v>90716</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>121476959</v>
       </c>
       <c r="B16" t="n">
-        <v>90737</v>
+        <v>90738</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121477102</v>
+        <v>121476802</v>
       </c>
       <c r="B17" t="n">
-        <v>78608</v>
+        <v>90716</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585517</v>
+        <v>585846</v>
       </c>
       <c r="R17" t="n">
-        <v>7268168</v>
+        <v>7268570</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121532739</v>
+        <v>121532743</v>
       </c>
       <c r="B18" t="n">
-        <v>90737</v>
+        <v>90738</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585910</v>
+        <v>585837</v>
       </c>
       <c r="R18" t="n">
-        <v>7268305</v>
+        <v>7268531</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2423,10 +2423,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121532642</v>
+        <v>121532587</v>
       </c>
       <c r="B19" t="n">
-        <v>90733</v>
+        <v>90716</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2439,21 +2439,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2467,10 +2467,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585595</v>
+        <v>585864</v>
       </c>
       <c r="R19" t="n">
-        <v>7268207</v>
+        <v>7268519</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2539,10 +2539,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121532587</v>
+        <v>121532741</v>
       </c>
       <c r="B20" t="n">
-        <v>90715</v>
+        <v>90738</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2555,21 +2555,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585864</v>
+        <v>585880</v>
       </c>
       <c r="R20" t="n">
-        <v>7268519</v>
+        <v>7268465</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2655,10 +2655,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121532890</v>
+        <v>121532896</v>
       </c>
       <c r="B21" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585516</v>
+        <v>585845</v>
       </c>
       <c r="R21" t="n">
-        <v>7268167</v>
+        <v>7268570</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2774,7 +2774,7 @@
         <v>121532738</v>
       </c>
       <c r="B22" t="n">
-        <v>90737</v>
+        <v>90738</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>121532260</v>
       </c>
       <c r="B23" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121532585</v>
+        <v>121532149</v>
       </c>
       <c r="B24" t="n">
-        <v>90715</v>
+        <v>91075</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3015,25 +3015,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>1506</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585516</v>
+        <v>585865</v>
       </c>
       <c r="R24" t="n">
-        <v>7268167</v>
+        <v>7268608</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3119,10 +3119,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121532894</v>
+        <v>121532588</v>
       </c>
       <c r="B25" t="n">
-        <v>78608</v>
+        <v>90716</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3135,21 +3135,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585864</v>
+        <v>585845</v>
       </c>
       <c r="R25" t="n">
-        <v>7268519</v>
+        <v>7268570</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3235,10 +3235,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121532473</v>
+        <v>121532739</v>
       </c>
       <c r="B26" t="n">
-        <v>91005</v>
+        <v>90738</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3251,21 +3251,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585865</v>
+        <v>585910</v>
       </c>
       <c r="R26" t="n">
-        <v>7268608</v>
+        <v>7268305</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3351,10 +3351,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121532165</v>
+        <v>121532890</v>
       </c>
       <c r="B27" t="n">
-        <v>77949</v>
+        <v>78609</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3363,25 +3363,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>498</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3395,10 +3395,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585864</v>
+        <v>585516</v>
       </c>
       <c r="R27" t="n">
-        <v>7268519</v>
+        <v>7268167</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3467,10 +3467,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121532743</v>
+        <v>121532473</v>
       </c>
       <c r="B28" t="n">
-        <v>90737</v>
+        <v>91006</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3483,21 +3483,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585837</v>
+        <v>585865</v>
       </c>
       <c r="R28" t="n">
-        <v>7268531</v>
+        <v>7268608</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3583,10 +3583,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121532149</v>
+        <v>121532165</v>
       </c>
       <c r="B29" t="n">
-        <v>91074</v>
+        <v>77950</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3599,21 +3599,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1506</v>
+        <v>498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585865</v>
+        <v>585864</v>
       </c>
       <c r="R29" t="n">
-        <v>7268608</v>
+        <v>7268519</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3699,10 +3699,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121532588</v>
+        <v>121532585</v>
       </c>
       <c r="B30" t="n">
-        <v>90715</v>
+        <v>90716</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3743,10 +3743,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585845</v>
+        <v>585516</v>
       </c>
       <c r="R30" t="n">
-        <v>7268570</v>
+        <v>7268167</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3815,10 +3815,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121532741</v>
+        <v>121532894</v>
       </c>
       <c r="B31" t="n">
-        <v>90737</v>
+        <v>78609</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3831,21 +3831,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585880</v>
+        <v>585864</v>
       </c>
       <c r="R31" t="n">
-        <v>7268465</v>
+        <v>7268519</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3931,10 +3931,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121532896</v>
+        <v>121532642</v>
       </c>
       <c r="B32" t="n">
-        <v>78608</v>
+        <v>90734</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3947,21 +3947,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585845</v>
+        <v>585595</v>
       </c>
       <c r="R32" t="n">
-        <v>7268570</v>
+        <v>7268207</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 31799-2020 artfynd.xlsx
+++ b/artfynd/A 31799-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121476691</v>
+        <v>121476384</v>
       </c>
       <c r="B2" t="n">
-        <v>91075</v>
+        <v>90720</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121476482</v>
+        <v>121477108</v>
       </c>
       <c r="B3" t="n">
-        <v>56568</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585919</v>
+        <v>585846</v>
       </c>
       <c r="R3" t="n">
-        <v>7268414</v>
+        <v>7268570</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121476857</v>
+        <v>121477106</v>
       </c>
       <c r="B4" t="n">
-        <v>90734</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585596</v>
+        <v>585865</v>
       </c>
       <c r="R4" t="n">
-        <v>7268207</v>
+        <v>7268520</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121477108</v>
+        <v>121476857</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>90734</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585846</v>
+        <v>585596</v>
       </c>
       <c r="R5" t="n">
-        <v>7268570</v>
+        <v>7268207</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121476960</v>
+        <v>121476956</v>
       </c>
       <c r="B6" t="n">
         <v>90738</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585838</v>
+        <v>585827</v>
       </c>
       <c r="R6" t="n">
-        <v>7268532</v>
+        <v>7268201</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121476384</v>
+        <v>121476960</v>
       </c>
       <c r="B8" t="n">
-        <v>90720</v>
+        <v>90738</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585866</v>
+        <v>585838</v>
       </c>
       <c r="R8" t="n">
-        <v>7268608</v>
+        <v>7268532</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121477106</v>
+        <v>121476801</v>
       </c>
       <c r="B9" t="n">
-        <v>78609</v>
+        <v>90716</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121477102</v>
+        <v>121476799</v>
       </c>
       <c r="B11" t="n">
-        <v>78609</v>
+        <v>90716</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121476799</v>
+        <v>121476959</v>
       </c>
       <c r="B12" t="n">
-        <v>90716</v>
+        <v>90738</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585517</v>
+        <v>585881</v>
       </c>
       <c r="R12" t="n">
-        <v>7268168</v>
+        <v>7268466</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121476956</v>
+        <v>121476482</v>
       </c>
       <c r="B13" t="n">
-        <v>90738</v>
+        <v>56568</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585827</v>
+        <v>585919</v>
       </c>
       <c r="R13" t="n">
-        <v>7268201</v>
+        <v>7268414</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121476957</v>
+        <v>121477102</v>
       </c>
       <c r="B14" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585911</v>
+        <v>585517</v>
       </c>
       <c r="R14" t="n">
-        <v>7268305</v>
+        <v>7268168</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121476801</v>
+        <v>121476802</v>
       </c>
       <c r="B15" t="n">
         <v>90716</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585865</v>
+        <v>585846</v>
       </c>
       <c r="R15" t="n">
-        <v>7268520</v>
+        <v>7268570</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121476959</v>
+        <v>121476691</v>
       </c>
       <c r="B16" t="n">
-        <v>90738</v>
+        <v>91075</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>1506</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585881</v>
+        <v>585866</v>
       </c>
       <c r="R16" t="n">
-        <v>7268466</v>
+        <v>7268608</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121476802</v>
+        <v>121476957</v>
       </c>
       <c r="B17" t="n">
-        <v>90716</v>
+        <v>90738</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585846</v>
+        <v>585911</v>
       </c>
       <c r="R17" t="n">
-        <v>7268570</v>
+        <v>7268305</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121532743</v>
+        <v>121532587</v>
       </c>
       <c r="B18" t="n">
-        <v>90738</v>
+        <v>90716</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585837</v>
+        <v>585864</v>
       </c>
       <c r="R18" t="n">
-        <v>7268531</v>
+        <v>7268519</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2423,10 +2423,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121532587</v>
+        <v>121532894</v>
       </c>
       <c r="B19" t="n">
-        <v>90716</v>
+        <v>78609</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2439,21 +2439,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2539,7 +2539,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121532741</v>
+        <v>121532743</v>
       </c>
       <c r="B20" t="n">
         <v>90738</v>
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585880</v>
+        <v>585837</v>
       </c>
       <c r="R20" t="n">
-        <v>7268465</v>
+        <v>7268531</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2655,10 +2655,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121532896</v>
+        <v>121532588</v>
       </c>
       <c r="B21" t="n">
-        <v>78609</v>
+        <v>90716</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2671,21 +2671,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2771,10 +2771,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121532738</v>
+        <v>121532642</v>
       </c>
       <c r="B22" t="n">
-        <v>90738</v>
+        <v>90734</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2787,21 +2787,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2815,10 +2815,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585826</v>
+        <v>585595</v>
       </c>
       <c r="R22" t="n">
-        <v>7268200</v>
+        <v>7268207</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2887,10 +2887,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121532260</v>
+        <v>121532739</v>
       </c>
       <c r="B23" t="n">
-        <v>90720</v>
+        <v>90738</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2903,21 +2903,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585865</v>
+        <v>585910</v>
       </c>
       <c r="R23" t="n">
-        <v>7268608</v>
+        <v>7268305</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121532149</v>
+        <v>121532260</v>
       </c>
       <c r="B24" t="n">
-        <v>91075</v>
+        <v>90720</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3015,25 +3015,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3119,10 +3119,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121532588</v>
+        <v>121532741</v>
       </c>
       <c r="B25" t="n">
-        <v>90716</v>
+        <v>90738</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3135,21 +3135,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585845</v>
+        <v>585880</v>
       </c>
       <c r="R25" t="n">
-        <v>7268570</v>
+        <v>7268465</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3235,10 +3235,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121532739</v>
+        <v>121532585</v>
       </c>
       <c r="B26" t="n">
-        <v>90738</v>
+        <v>90716</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3251,21 +3251,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585910</v>
+        <v>585516</v>
       </c>
       <c r="R26" t="n">
-        <v>7268305</v>
+        <v>7268167</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3351,10 +3351,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121532890</v>
+        <v>121532165</v>
       </c>
       <c r="B27" t="n">
-        <v>78609</v>
+        <v>77950</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3363,25 +3363,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3395,10 +3395,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585516</v>
+        <v>585864</v>
       </c>
       <c r="R27" t="n">
-        <v>7268167</v>
+        <v>7268519</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3467,10 +3467,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121532473</v>
+        <v>121532149</v>
       </c>
       <c r="B28" t="n">
-        <v>91006</v>
+        <v>91075</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3479,25 +3479,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>1506</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3583,10 +3583,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121532165</v>
+        <v>121532473</v>
       </c>
       <c r="B29" t="n">
-        <v>77950</v>
+        <v>91006</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3595,25 +3595,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>498</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585864</v>
+        <v>585865</v>
       </c>
       <c r="R29" t="n">
-        <v>7268519</v>
+        <v>7268608</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3699,10 +3699,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121532585</v>
+        <v>121532738</v>
       </c>
       <c r="B30" t="n">
-        <v>90716</v>
+        <v>90738</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3715,21 +3715,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3743,10 +3743,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585516</v>
+        <v>585826</v>
       </c>
       <c r="R30" t="n">
-        <v>7268167</v>
+        <v>7268200</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3815,7 +3815,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121532894</v>
+        <v>121532896</v>
       </c>
       <c r="B31" t="n">
         <v>78609</v>
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585864</v>
+        <v>585845</v>
       </c>
       <c r="R31" t="n">
-        <v>7268519</v>
+        <v>7268570</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3931,10 +3931,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121532642</v>
+        <v>121532890</v>
       </c>
       <c r="B32" t="n">
-        <v>90734</v>
+        <v>78609</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3947,21 +3947,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585595</v>
+        <v>585516</v>
       </c>
       <c r="R32" t="n">
-        <v>7268207</v>
+        <v>7268167</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 31799-2020 artfynd.xlsx
+++ b/artfynd/A 31799-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121476384</v>
+        <v>121476959</v>
       </c>
       <c r="B2" t="n">
-        <v>90720</v>
+        <v>90738</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585866</v>
+        <v>585881</v>
       </c>
       <c r="R2" t="n">
-        <v>7268608</v>
+        <v>7268466</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121477108</v>
+        <v>121476482</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>56568</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585846</v>
+        <v>585919</v>
       </c>
       <c r="R3" t="n">
-        <v>7268570</v>
+        <v>7268414</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121477106</v>
+        <v>121476799</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>90716</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585865</v>
+        <v>585517</v>
       </c>
       <c r="R4" t="n">
-        <v>7268520</v>
+        <v>7268168</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121476857</v>
+        <v>121476725</v>
       </c>
       <c r="B5" t="n">
-        <v>90734</v>
+        <v>77950</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585596</v>
+        <v>585865</v>
       </c>
       <c r="R5" t="n">
-        <v>7268207</v>
+        <v>7268520</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121476956</v>
+        <v>121476957</v>
       </c>
       <c r="B6" t="n">
         <v>90738</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585827</v>
+        <v>585911</v>
       </c>
       <c r="R6" t="n">
-        <v>7268201</v>
+        <v>7268305</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121476645</v>
+        <v>121476960</v>
       </c>
       <c r="B7" t="n">
-        <v>91006</v>
+        <v>90738</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585866</v>
+        <v>585838</v>
       </c>
       <c r="R7" t="n">
-        <v>7268608</v>
+        <v>7268532</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121476960</v>
+        <v>121476802</v>
       </c>
       <c r="B8" t="n">
-        <v>90738</v>
+        <v>90716</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585838</v>
+        <v>585846</v>
       </c>
       <c r="R8" t="n">
-        <v>7268532</v>
+        <v>7268570</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121476801</v>
+        <v>121476691</v>
       </c>
       <c r="B9" t="n">
-        <v>90716</v>
+        <v>91075</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>1506</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585865</v>
+        <v>585866</v>
       </c>
       <c r="R9" t="n">
-        <v>7268520</v>
+        <v>7268608</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121476725</v>
+        <v>121476857</v>
       </c>
       <c r="B10" t="n">
-        <v>77950</v>
+        <v>90734</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>498</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585865</v>
+        <v>585596</v>
       </c>
       <c r="R10" t="n">
-        <v>7268520</v>
+        <v>7268207</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121476799</v>
+        <v>121476801</v>
       </c>
       <c r="B11" t="n">
         <v>90716</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585517</v>
+        <v>585865</v>
       </c>
       <c r="R11" t="n">
-        <v>7268168</v>
+        <v>7268520</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121476959</v>
+        <v>121476384</v>
       </c>
       <c r="B12" t="n">
-        <v>90738</v>
+        <v>90720</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585881</v>
+        <v>585866</v>
       </c>
       <c r="R12" t="n">
-        <v>7268466</v>
+        <v>7268608</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121476482</v>
+        <v>121476956</v>
       </c>
       <c r="B13" t="n">
-        <v>56568</v>
+        <v>90738</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585919</v>
+        <v>585827</v>
       </c>
       <c r="R13" t="n">
-        <v>7268414</v>
+        <v>7268201</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121477102</v>
+        <v>121477108</v>
       </c>
       <c r="B14" t="n">
         <v>78609</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585517</v>
+        <v>585846</v>
       </c>
       <c r="R14" t="n">
-        <v>7268168</v>
+        <v>7268570</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121476802</v>
+        <v>121476645</v>
       </c>
       <c r="B15" t="n">
-        <v>90716</v>
+        <v>91006</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585846</v>
+        <v>585866</v>
       </c>
       <c r="R15" t="n">
-        <v>7268570</v>
+        <v>7268608</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121476691</v>
+        <v>121477102</v>
       </c>
       <c r="B16" t="n">
-        <v>91075</v>
+        <v>78609</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585866</v>
+        <v>585517</v>
       </c>
       <c r="R16" t="n">
-        <v>7268608</v>
+        <v>7268168</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121476957</v>
+        <v>121477106</v>
       </c>
       <c r="B17" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585911</v>
+        <v>585865</v>
       </c>
       <c r="R17" t="n">
-        <v>7268305</v>
+        <v>7268520</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121532587</v>
+        <v>121532738</v>
       </c>
       <c r="B18" t="n">
-        <v>90716</v>
+        <v>90738</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585864</v>
+        <v>585826</v>
       </c>
       <c r="R18" t="n">
-        <v>7268519</v>
+        <v>7268200</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2423,7 +2423,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121532894</v>
+        <v>121532890</v>
       </c>
       <c r="B19" t="n">
         <v>78609</v>
@@ -2467,10 +2467,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585864</v>
+        <v>585516</v>
       </c>
       <c r="R19" t="n">
-        <v>7268519</v>
+        <v>7268167</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2539,10 +2539,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121532743</v>
+        <v>121532149</v>
       </c>
       <c r="B20" t="n">
-        <v>90738</v>
+        <v>91075</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2551,25 +2551,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>1506</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585837</v>
+        <v>585865</v>
       </c>
       <c r="R20" t="n">
-        <v>7268531</v>
+        <v>7268608</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2655,10 +2655,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121532588</v>
+        <v>121532739</v>
       </c>
       <c r="B21" t="n">
-        <v>90716</v>
+        <v>90738</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2671,21 +2671,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585845</v>
+        <v>585910</v>
       </c>
       <c r="R21" t="n">
-        <v>7268570</v>
+        <v>7268305</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2771,10 +2771,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121532642</v>
+        <v>121532585</v>
       </c>
       <c r="B22" t="n">
-        <v>90734</v>
+        <v>90716</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2787,21 +2787,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2815,10 +2815,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585595</v>
+        <v>585516</v>
       </c>
       <c r="R22" t="n">
-        <v>7268207</v>
+        <v>7268167</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2887,7 +2887,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121532739</v>
+        <v>121532741</v>
       </c>
       <c r="B23" t="n">
         <v>90738</v>
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585910</v>
+        <v>585880</v>
       </c>
       <c r="R23" t="n">
-        <v>7268305</v>
+        <v>7268465</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3003,10 +3003,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121532260</v>
+        <v>121532894</v>
       </c>
       <c r="B24" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3019,21 +3019,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585865</v>
+        <v>585864</v>
       </c>
       <c r="R24" t="n">
-        <v>7268608</v>
+        <v>7268519</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3119,10 +3119,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121532741</v>
+        <v>121532473</v>
       </c>
       <c r="B25" t="n">
-        <v>90738</v>
+        <v>91006</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3135,21 +3135,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585880</v>
+        <v>585865</v>
       </c>
       <c r="R25" t="n">
-        <v>7268465</v>
+        <v>7268608</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3235,7 +3235,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121532585</v>
+        <v>121532587</v>
       </c>
       <c r="B26" t="n">
         <v>90716</v>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585516</v>
+        <v>585864</v>
       </c>
       <c r="R26" t="n">
-        <v>7268167</v>
+        <v>7268519</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3467,10 +3467,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121532149</v>
+        <v>121532642</v>
       </c>
       <c r="B28" t="n">
-        <v>91075</v>
+        <v>90734</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3479,25 +3479,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1506</v>
+        <v>1204</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585865</v>
+        <v>585595</v>
       </c>
       <c r="R28" t="n">
-        <v>7268608</v>
+        <v>7268207</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3583,10 +3583,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121532473</v>
+        <v>121532743</v>
       </c>
       <c r="B29" t="n">
-        <v>91006</v>
+        <v>90738</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3599,21 +3599,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585865</v>
+        <v>585837</v>
       </c>
       <c r="R29" t="n">
-        <v>7268608</v>
+        <v>7268531</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3699,10 +3699,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121532738</v>
+        <v>121532588</v>
       </c>
       <c r="B30" t="n">
-        <v>90738</v>
+        <v>90716</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3715,21 +3715,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3743,10 +3743,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585826</v>
+        <v>585845</v>
       </c>
       <c r="R30" t="n">
-        <v>7268200</v>
+        <v>7268570</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3815,10 +3815,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121532896</v>
+        <v>121532260</v>
       </c>
       <c r="B31" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3831,21 +3831,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585845</v>
+        <v>585865</v>
       </c>
       <c r="R31" t="n">
-        <v>7268570</v>
+        <v>7268608</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3931,7 +3931,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121532890</v>
+        <v>121532896</v>
       </c>
       <c r="B32" t="n">
         <v>78609</v>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585516</v>
+        <v>585845</v>
       </c>
       <c r="R32" t="n">
-        <v>7268167</v>
+        <v>7268570</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 31799-2020 artfynd.xlsx
+++ b/artfynd/A 31799-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121476959</v>
+        <v>121476691</v>
       </c>
       <c r="B2" t="n">
-        <v>90738</v>
+        <v>91075</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1506</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585881</v>
+        <v>585866</v>
       </c>
       <c r="R2" t="n">
-        <v>7268466</v>
+        <v>7268608</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121476482</v>
+        <v>121476857</v>
       </c>
       <c r="B3" t="n">
-        <v>56568</v>
+        <v>90734</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585919</v>
+        <v>585596</v>
       </c>
       <c r="R3" t="n">
-        <v>7268414</v>
+        <v>7268207</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121476799</v>
+        <v>121476802</v>
       </c>
       <c r="B4" t="n">
         <v>90716</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585517</v>
+        <v>585846</v>
       </c>
       <c r="R4" t="n">
-        <v>7268168</v>
+        <v>7268570</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121476725</v>
+        <v>121477108</v>
       </c>
       <c r="B5" t="n">
-        <v>77950</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>498</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585865</v>
+        <v>585846</v>
       </c>
       <c r="R5" t="n">
-        <v>7268520</v>
+        <v>7268570</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121476957</v>
+        <v>121476645</v>
       </c>
       <c r="B6" t="n">
-        <v>90738</v>
+        <v>91006</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585911</v>
+        <v>585866</v>
       </c>
       <c r="R6" t="n">
-        <v>7268305</v>
+        <v>7268608</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121476960</v>
+        <v>121476956</v>
       </c>
       <c r="B7" t="n">
         <v>90738</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585838</v>
+        <v>585827</v>
       </c>
       <c r="R7" t="n">
-        <v>7268532</v>
+        <v>7268201</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121476802</v>
+        <v>121476482</v>
       </c>
       <c r="B8" t="n">
-        <v>90716</v>
+        <v>56568</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585846</v>
+        <v>585919</v>
       </c>
       <c r="R8" t="n">
-        <v>7268570</v>
+        <v>7268414</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121476691</v>
+        <v>121476801</v>
       </c>
       <c r="B9" t="n">
-        <v>91075</v>
+        <v>90716</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1506</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585866</v>
+        <v>585865</v>
       </c>
       <c r="R9" t="n">
-        <v>7268608</v>
+        <v>7268520</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121476857</v>
+        <v>121476384</v>
       </c>
       <c r="B10" t="n">
-        <v>90734</v>
+        <v>90720</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585596</v>
+        <v>585866</v>
       </c>
       <c r="R10" t="n">
-        <v>7268207</v>
+        <v>7268608</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121476801</v>
+        <v>121477106</v>
       </c>
       <c r="B11" t="n">
-        <v>90716</v>
+        <v>78609</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121476384</v>
+        <v>121476959</v>
       </c>
       <c r="B12" t="n">
-        <v>90720</v>
+        <v>90738</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585866</v>
+        <v>585881</v>
       </c>
       <c r="R12" t="n">
-        <v>7268608</v>
+        <v>7268466</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121476956</v>
+        <v>121476799</v>
       </c>
       <c r="B13" t="n">
-        <v>90738</v>
+        <v>90716</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585827</v>
+        <v>585517</v>
       </c>
       <c r="R13" t="n">
-        <v>7268201</v>
+        <v>7268168</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121477108</v>
+        <v>121476957</v>
       </c>
       <c r="B14" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585846</v>
+        <v>585911</v>
       </c>
       <c r="R14" t="n">
-        <v>7268570</v>
+        <v>7268305</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121476645</v>
+        <v>121476960</v>
       </c>
       <c r="B15" t="n">
-        <v>91006</v>
+        <v>90738</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585866</v>
+        <v>585838</v>
       </c>
       <c r="R15" t="n">
-        <v>7268608</v>
+        <v>7268532</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121477102</v>
+        <v>121476725</v>
       </c>
       <c r="B16" t="n">
-        <v>78609</v>
+        <v>77950</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585517</v>
+        <v>585865</v>
       </c>
       <c r="R16" t="n">
-        <v>7268168</v>
+        <v>7268520</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121477106</v>
+        <v>121477102</v>
       </c>
       <c r="B17" t="n">
         <v>78609</v>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585865</v>
+        <v>585517</v>
       </c>
       <c r="R17" t="n">
-        <v>7268520</v>
+        <v>7268168</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2423,7 +2423,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121532890</v>
+        <v>121532894</v>
       </c>
       <c r="B19" t="n">
         <v>78609</v>
@@ -2467,10 +2467,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585516</v>
+        <v>585864</v>
       </c>
       <c r="R19" t="n">
-        <v>7268167</v>
+        <v>7268519</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2539,10 +2539,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121532149</v>
+        <v>121532588</v>
       </c>
       <c r="B20" t="n">
-        <v>91075</v>
+        <v>90716</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2551,25 +2551,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1506</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585865</v>
+        <v>585845</v>
       </c>
       <c r="R20" t="n">
-        <v>7268608</v>
+        <v>7268570</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2655,10 +2655,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121532739</v>
+        <v>121532260</v>
       </c>
       <c r="B21" t="n">
-        <v>90738</v>
+        <v>90720</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2671,21 +2671,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585910</v>
+        <v>585865</v>
       </c>
       <c r="R21" t="n">
-        <v>7268305</v>
+        <v>7268608</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2771,10 +2771,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121532585</v>
+        <v>121532739</v>
       </c>
       <c r="B22" t="n">
-        <v>90716</v>
+        <v>90738</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2787,21 +2787,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2815,10 +2815,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585516</v>
+        <v>585910</v>
       </c>
       <c r="R22" t="n">
-        <v>7268167</v>
+        <v>7268305</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2887,7 +2887,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121532741</v>
+        <v>121532743</v>
       </c>
       <c r="B23" t="n">
         <v>90738</v>
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585880</v>
+        <v>585837</v>
       </c>
       <c r="R23" t="n">
-        <v>7268465</v>
+        <v>7268531</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3003,10 +3003,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121532894</v>
+        <v>121532585</v>
       </c>
       <c r="B24" t="n">
-        <v>78609</v>
+        <v>90716</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3019,21 +3019,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585864</v>
+        <v>585516</v>
       </c>
       <c r="R24" t="n">
-        <v>7268519</v>
+        <v>7268167</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3119,10 +3119,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121532473</v>
+        <v>121532587</v>
       </c>
       <c r="B25" t="n">
-        <v>91006</v>
+        <v>90716</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3135,21 +3135,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585865</v>
+        <v>585864</v>
       </c>
       <c r="R25" t="n">
-        <v>7268608</v>
+        <v>7268519</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3235,10 +3235,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121532587</v>
+        <v>121532890</v>
       </c>
       <c r="B26" t="n">
-        <v>90716</v>
+        <v>78609</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3251,21 +3251,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585864</v>
+        <v>585516</v>
       </c>
       <c r="R26" t="n">
-        <v>7268519</v>
+        <v>7268167</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3351,10 +3351,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121532165</v>
+        <v>121532642</v>
       </c>
       <c r="B27" t="n">
-        <v>77950</v>
+        <v>90734</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3363,25 +3363,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>498</v>
+        <v>1204</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3395,10 +3395,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585864</v>
+        <v>585595</v>
       </c>
       <c r="R27" t="n">
-        <v>7268519</v>
+        <v>7268207</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3467,10 +3467,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121532642</v>
+        <v>121532149</v>
       </c>
       <c r="B28" t="n">
-        <v>90734</v>
+        <v>91075</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3479,25 +3479,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1204</v>
+        <v>1506</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585595</v>
+        <v>585865</v>
       </c>
       <c r="R28" t="n">
-        <v>7268207</v>
+        <v>7268608</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3583,7 +3583,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121532743</v>
+        <v>121532741</v>
       </c>
       <c r="B29" t="n">
         <v>90738</v>
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585837</v>
+        <v>585880</v>
       </c>
       <c r="R29" t="n">
-        <v>7268531</v>
+        <v>7268465</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3699,10 +3699,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121532588</v>
+        <v>121532165</v>
       </c>
       <c r="B30" t="n">
-        <v>90716</v>
+        <v>77950</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3711,25 +3711,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3743,10 +3743,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585845</v>
+        <v>585864</v>
       </c>
       <c r="R30" t="n">
-        <v>7268570</v>
+        <v>7268519</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3815,10 +3815,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121532260</v>
+        <v>121532473</v>
       </c>
       <c r="B31" t="n">
-        <v>90720</v>
+        <v>91006</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3831,21 +3831,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 31799-2020 artfynd.xlsx
+++ b/artfynd/A 31799-2020 artfynd.xlsx
@@ -3467,10 +3467,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121532149</v>
+        <v>121532741</v>
       </c>
       <c r="B28" t="n">
-        <v>91075</v>
+        <v>90738</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3479,25 +3479,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1506</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585865</v>
+        <v>585880</v>
       </c>
       <c r="R28" t="n">
-        <v>7268608</v>
+        <v>7268465</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3583,10 +3583,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121532741</v>
+        <v>121532149</v>
       </c>
       <c r="B29" t="n">
-        <v>90738</v>
+        <v>91075</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3595,25 +3595,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1506</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585880</v>
+        <v>585865</v>
       </c>
       <c r="R29" t="n">
-        <v>7268465</v>
+        <v>7268608</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 31799-2020 artfynd.xlsx
+++ b/artfynd/A 31799-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121476691</v>
+        <v>121476959</v>
       </c>
       <c r="B2" t="n">
-        <v>91075</v>
+        <v>90746</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1506</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585866</v>
+        <v>585881</v>
       </c>
       <c r="R2" t="n">
-        <v>7268608</v>
+        <v>7268466</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121476857</v>
+        <v>121477108</v>
       </c>
       <c r="B3" t="n">
-        <v>90734</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585596</v>
+        <v>585846</v>
       </c>
       <c r="R3" t="n">
-        <v>7268207</v>
+        <v>7268570</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121476802</v>
+        <v>121476691</v>
       </c>
       <c r="B4" t="n">
-        <v>90716</v>
+        <v>91083</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>1506</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585846</v>
+        <v>585866</v>
       </c>
       <c r="R4" t="n">
-        <v>7268570</v>
+        <v>7268608</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121477108</v>
+        <v>121476801</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>90724</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585846</v>
+        <v>585865</v>
       </c>
       <c r="R5" t="n">
-        <v>7268570</v>
+        <v>7268520</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121476645</v>
+        <v>121476802</v>
       </c>
       <c r="B6" t="n">
-        <v>91006</v>
+        <v>90724</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585866</v>
+        <v>585846</v>
       </c>
       <c r="R6" t="n">
-        <v>7268608</v>
+        <v>7268570</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121476956</v>
+        <v>121476725</v>
       </c>
       <c r="B7" t="n">
-        <v>90738</v>
+        <v>77957</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585827</v>
+        <v>585865</v>
       </c>
       <c r="R7" t="n">
-        <v>7268201</v>
+        <v>7268520</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121476482</v>
+        <v>121476956</v>
       </c>
       <c r="B8" t="n">
-        <v>56568</v>
+        <v>90746</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585919</v>
+        <v>585827</v>
       </c>
       <c r="R8" t="n">
-        <v>7268414</v>
+        <v>7268201</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121476801</v>
+        <v>121477102</v>
       </c>
       <c r="B9" t="n">
-        <v>90716</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585865</v>
+        <v>585517</v>
       </c>
       <c r="R9" t="n">
-        <v>7268520</v>
+        <v>7268168</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121476384</v>
+        <v>121476857</v>
       </c>
       <c r="B10" t="n">
-        <v>90720</v>
+        <v>90742</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585866</v>
+        <v>585596</v>
       </c>
       <c r="R10" t="n">
-        <v>7268608</v>
+        <v>7268207</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121477106</v>
+        <v>121476957</v>
       </c>
       <c r="B11" t="n">
-        <v>78609</v>
+        <v>90746</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585865</v>
+        <v>585911</v>
       </c>
       <c r="R11" t="n">
-        <v>7268520</v>
+        <v>7268305</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121476959</v>
+        <v>121476384</v>
       </c>
       <c r="B12" t="n">
-        <v>90738</v>
+        <v>90728</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585881</v>
+        <v>585866</v>
       </c>
       <c r="R12" t="n">
-        <v>7268466</v>
+        <v>7268608</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121476799</v>
+        <v>121476645</v>
       </c>
       <c r="B13" t="n">
-        <v>90716</v>
+        <v>91014</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585517</v>
+        <v>585866</v>
       </c>
       <c r="R13" t="n">
-        <v>7268168</v>
+        <v>7268608</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121476957</v>
+        <v>121477106</v>
       </c>
       <c r="B14" t="n">
-        <v>90738</v>
+        <v>78616</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585911</v>
+        <v>585865</v>
       </c>
       <c r="R14" t="n">
-        <v>7268305</v>
+        <v>7268520</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121476960</v>
+        <v>121476799</v>
       </c>
       <c r="B15" t="n">
-        <v>90738</v>
+        <v>90724</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585838</v>
+        <v>585517</v>
       </c>
       <c r="R15" t="n">
-        <v>7268532</v>
+        <v>7268168</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121476725</v>
+        <v>121476960</v>
       </c>
       <c r="B16" t="n">
-        <v>77950</v>
+        <v>90746</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>498</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585865</v>
+        <v>585838</v>
       </c>
       <c r="R16" t="n">
-        <v>7268520</v>
+        <v>7268532</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121477102</v>
+        <v>121476482</v>
       </c>
       <c r="B17" t="n">
-        <v>78609</v>
+        <v>56569</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585517</v>
+        <v>585919</v>
       </c>
       <c r="R17" t="n">
-        <v>7268168</v>
+        <v>7268414</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2310,7 +2310,7 @@
         <v>121532738</v>
       </c>
       <c r="B18" t="n">
-        <v>90738</v>
+        <v>90746</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121532894</v>
+        <v>121532165</v>
       </c>
       <c r="B19" t="n">
-        <v>78609</v>
+        <v>77957</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2435,25 +2435,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2539,10 +2539,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121532588</v>
+        <v>121532642</v>
       </c>
       <c r="B20" t="n">
-        <v>90716</v>
+        <v>90742</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2555,21 +2555,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585845</v>
+        <v>585595</v>
       </c>
       <c r="R20" t="n">
-        <v>7268570</v>
+        <v>7268207</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2655,10 +2655,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121532260</v>
+        <v>121532896</v>
       </c>
       <c r="B21" t="n">
-        <v>90720</v>
+        <v>78616</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2671,21 +2671,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585865</v>
+        <v>585845</v>
       </c>
       <c r="R21" t="n">
-        <v>7268608</v>
+        <v>7268570</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2771,10 +2771,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121532739</v>
+        <v>121532587</v>
       </c>
       <c r="B22" t="n">
-        <v>90738</v>
+        <v>90724</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2787,21 +2787,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2815,10 +2815,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585910</v>
+        <v>585864</v>
       </c>
       <c r="R22" t="n">
-        <v>7268305</v>
+        <v>7268519</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2887,10 +2887,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121532743</v>
+        <v>121532894</v>
       </c>
       <c r="B23" t="n">
-        <v>90738</v>
+        <v>78616</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2903,21 +2903,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585837</v>
+        <v>585864</v>
       </c>
       <c r="R23" t="n">
-        <v>7268531</v>
+        <v>7268519</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121532585</v>
+        <v>121532260</v>
       </c>
       <c r="B24" t="n">
-        <v>90716</v>
+        <v>90728</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3019,21 +3019,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585516</v>
+        <v>585865</v>
       </c>
       <c r="R24" t="n">
-        <v>7268167</v>
+        <v>7268608</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3119,10 +3119,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121532587</v>
+        <v>121532741</v>
       </c>
       <c r="B25" t="n">
-        <v>90716</v>
+        <v>90746</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3135,21 +3135,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585864</v>
+        <v>585880</v>
       </c>
       <c r="R25" t="n">
-        <v>7268519</v>
+        <v>7268465</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3238,7 +3238,7 @@
         <v>121532890</v>
       </c>
       <c r="B26" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3351,10 +3351,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121532642</v>
+        <v>121532149</v>
       </c>
       <c r="B27" t="n">
-        <v>90734</v>
+        <v>91083</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3363,25 +3363,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1204</v>
+        <v>1506</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3395,10 +3395,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585595</v>
+        <v>585865</v>
       </c>
       <c r="R27" t="n">
-        <v>7268207</v>
+        <v>7268608</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3467,10 +3467,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121532741</v>
+        <v>121532739</v>
       </c>
       <c r="B28" t="n">
-        <v>90738</v>
+        <v>90746</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585880</v>
+        <v>585910</v>
       </c>
       <c r="R28" t="n">
-        <v>7268465</v>
+        <v>7268305</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3583,10 +3583,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121532149</v>
+        <v>121532585</v>
       </c>
       <c r="B29" t="n">
-        <v>91075</v>
+        <v>90724</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3595,25 +3595,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1506</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585865</v>
+        <v>585516</v>
       </c>
       <c r="R29" t="n">
-        <v>7268608</v>
+        <v>7268167</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3699,10 +3699,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121532165</v>
+        <v>121532743</v>
       </c>
       <c r="B30" t="n">
-        <v>77950</v>
+        <v>90746</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3711,25 +3711,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>498</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3743,10 +3743,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585864</v>
+        <v>585837</v>
       </c>
       <c r="R30" t="n">
-        <v>7268519</v>
+        <v>7268531</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3818,7 +3818,7 @@
         <v>121532473</v>
       </c>
       <c r="B31" t="n">
-        <v>91006</v>
+        <v>91014</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3931,10 +3931,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121532896</v>
+        <v>121532588</v>
       </c>
       <c r="B32" t="n">
-        <v>78609</v>
+        <v>90724</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3947,21 +3947,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 31799-2020 artfynd.xlsx
+++ b/artfynd/A 31799-2020 artfynd.xlsx
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121476960</v>
+        <v>121476482</v>
       </c>
       <c r="B16" t="n">
-        <v>90746</v>
+        <v>56569</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585838</v>
+        <v>585919</v>
       </c>
       <c r="R16" t="n">
-        <v>7268532</v>
+        <v>7268414</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121476482</v>
+        <v>121476960</v>
       </c>
       <c r="B17" t="n">
-        <v>56569</v>
+        <v>90746</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585919</v>
+        <v>585838</v>
       </c>
       <c r="R17" t="n">
-        <v>7268414</v>
+        <v>7268532</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 31799-2020 artfynd.xlsx
+++ b/artfynd/A 31799-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121476956</v>
+        <v>121476801</v>
       </c>
       <c r="B2" t="n">
-        <v>90746</v>
+        <v>90724</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585827</v>
+        <v>585865</v>
       </c>
       <c r="R2" t="n">
-        <v>7268201</v>
+        <v>7268520</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121476384</v>
+        <v>121476691</v>
       </c>
       <c r="B3" t="n">
-        <v>90728</v>
+        <v>91083</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1506</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121476802</v>
+        <v>121476857</v>
       </c>
       <c r="B4" t="n">
-        <v>90724</v>
+        <v>90742</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585846</v>
+        <v>585596</v>
       </c>
       <c r="R4" t="n">
-        <v>7268570</v>
+        <v>7268207</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121476725</v>
+        <v>121476799</v>
       </c>
       <c r="B5" t="n">
-        <v>77957</v>
+        <v>90724</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>498</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585865</v>
+        <v>585517</v>
       </c>
       <c r="R5" t="n">
-        <v>7268520</v>
+        <v>7268168</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121476645</v>
+        <v>121476959</v>
       </c>
       <c r="B7" t="n">
-        <v>91014</v>
+        <v>90746</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585866</v>
+        <v>585881</v>
       </c>
       <c r="R7" t="n">
-        <v>7268608</v>
+        <v>7268466</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121476959</v>
+        <v>121476960</v>
       </c>
       <c r="B8" t="n">
         <v>90746</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585881</v>
+        <v>585838</v>
       </c>
       <c r="R8" t="n">
-        <v>7268466</v>
+        <v>7268532</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121476799</v>
+        <v>121477108</v>
       </c>
       <c r="B9" t="n">
-        <v>90724</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585517</v>
+        <v>585846</v>
       </c>
       <c r="R9" t="n">
-        <v>7268168</v>
+        <v>7268570</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121477106</v>
+        <v>121476725</v>
       </c>
       <c r="B10" t="n">
-        <v>78616</v>
+        <v>77957</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121476960</v>
+        <v>121476957</v>
       </c>
       <c r="B11" t="n">
         <v>90746</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585838</v>
+        <v>585911</v>
       </c>
       <c r="R11" t="n">
-        <v>7268532</v>
+        <v>7268305</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121476857</v>
+        <v>121476384</v>
       </c>
       <c r="B12" t="n">
-        <v>90742</v>
+        <v>90728</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585596</v>
+        <v>585866</v>
       </c>
       <c r="R12" t="n">
-        <v>7268207</v>
+        <v>7268608</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121476801</v>
+        <v>121476645</v>
       </c>
       <c r="B13" t="n">
-        <v>90724</v>
+        <v>91014</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585865</v>
+        <v>585866</v>
       </c>
       <c r="R13" t="n">
-        <v>7268520</v>
+        <v>7268608</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121476957</v>
+        <v>121477106</v>
       </c>
       <c r="B15" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585911</v>
+        <v>585865</v>
       </c>
       <c r="R15" t="n">
-        <v>7268305</v>
+        <v>7268520</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121476691</v>
+        <v>121476956</v>
       </c>
       <c r="B16" t="n">
-        <v>91083</v>
+        <v>90746</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1506</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585866</v>
+        <v>585827</v>
       </c>
       <c r="R16" t="n">
-        <v>7268608</v>
+        <v>7268201</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121477108</v>
+        <v>121476802</v>
       </c>
       <c r="B17" t="n">
-        <v>78616</v>
+        <v>90724</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121532585</v>
+        <v>121532896</v>
       </c>
       <c r="B18" t="n">
-        <v>90724</v>
+        <v>78616</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585516</v>
+        <v>585845</v>
       </c>
       <c r="R18" t="n">
-        <v>7268167</v>
+        <v>7268570</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2423,10 +2423,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121532587</v>
+        <v>121532894</v>
       </c>
       <c r="B19" t="n">
-        <v>90724</v>
+        <v>78616</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2439,21 +2439,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2655,10 +2655,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121532165</v>
+        <v>121532739</v>
       </c>
       <c r="B21" t="n">
-        <v>77957</v>
+        <v>90746</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2667,25 +2667,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>498</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585864</v>
+        <v>585910</v>
       </c>
       <c r="R21" t="n">
-        <v>7268519</v>
+        <v>7268305</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2771,7 +2771,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121532743</v>
+        <v>121532738</v>
       </c>
       <c r="B22" t="n">
         <v>90746</v>
@@ -2815,10 +2815,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585837</v>
+        <v>585826</v>
       </c>
       <c r="R22" t="n">
-        <v>7268531</v>
+        <v>7268200</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2887,10 +2887,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121532473</v>
+        <v>121532890</v>
       </c>
       <c r="B23" t="n">
-        <v>91014</v>
+        <v>78616</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2903,21 +2903,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585865</v>
+        <v>585516</v>
       </c>
       <c r="R23" t="n">
-        <v>7268608</v>
+        <v>7268167</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3003,10 +3003,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121532642</v>
+        <v>121532473</v>
       </c>
       <c r="B24" t="n">
-        <v>90742</v>
+        <v>91014</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3019,21 +3019,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585595</v>
+        <v>585865</v>
       </c>
       <c r="R24" t="n">
-        <v>7268207</v>
+        <v>7268608</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3119,10 +3119,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121532896</v>
+        <v>121532165</v>
       </c>
       <c r="B25" t="n">
-        <v>78616</v>
+        <v>77957</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3131,25 +3131,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585845</v>
+        <v>585864</v>
       </c>
       <c r="R25" t="n">
-        <v>7268570</v>
+        <v>7268519</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3235,10 +3235,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121532890</v>
+        <v>121532585</v>
       </c>
       <c r="B26" t="n">
-        <v>78616</v>
+        <v>90724</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3251,21 +3251,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3351,10 +3351,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121532149</v>
+        <v>121532741</v>
       </c>
       <c r="B27" t="n">
-        <v>91083</v>
+        <v>90746</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3363,25 +3363,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1506</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3395,10 +3395,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585865</v>
+        <v>585880</v>
       </c>
       <c r="R27" t="n">
-        <v>7268608</v>
+        <v>7268465</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3467,10 +3467,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121532588</v>
+        <v>121532743</v>
       </c>
       <c r="B28" t="n">
-        <v>90724</v>
+        <v>90746</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3483,21 +3483,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585845</v>
+        <v>585837</v>
       </c>
       <c r="R28" t="n">
-        <v>7268570</v>
+        <v>7268531</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3583,10 +3583,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121532894</v>
+        <v>121532642</v>
       </c>
       <c r="B29" t="n">
-        <v>78616</v>
+        <v>90742</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3599,21 +3599,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585864</v>
+        <v>585595</v>
       </c>
       <c r="R29" t="n">
-        <v>7268519</v>
+        <v>7268207</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3699,10 +3699,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121532739</v>
+        <v>121532588</v>
       </c>
       <c r="B30" t="n">
-        <v>90746</v>
+        <v>90724</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3715,21 +3715,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3743,10 +3743,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585910</v>
+        <v>585845</v>
       </c>
       <c r="R30" t="n">
-        <v>7268305</v>
+        <v>7268570</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3815,10 +3815,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121532738</v>
+        <v>121532587</v>
       </c>
       <c r="B31" t="n">
-        <v>90746</v>
+        <v>90724</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3831,21 +3831,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585826</v>
+        <v>585864</v>
       </c>
       <c r="R31" t="n">
-        <v>7268200</v>
+        <v>7268519</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3931,10 +3931,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121532741</v>
+        <v>121532149</v>
       </c>
       <c r="B32" t="n">
-        <v>90746</v>
+        <v>91083</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3943,25 +3943,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>1506</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585880</v>
+        <v>585865</v>
       </c>
       <c r="R32" t="n">
-        <v>7268465</v>
+        <v>7268608</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 31799-2020 artfynd.xlsx
+++ b/artfynd/A 31799-2020 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121476857</v>
+        <v>121476799</v>
       </c>
       <c r="B4" t="n">
-        <v>90742</v>
+        <v>90724</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585596</v>
+        <v>585517</v>
       </c>
       <c r="R4" t="n">
-        <v>7268207</v>
+        <v>7268168</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121476799</v>
+        <v>121476857</v>
       </c>
       <c r="B5" t="n">
-        <v>90724</v>
+        <v>90742</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585517</v>
+        <v>585596</v>
       </c>
       <c r="R5" t="n">
-        <v>7268168</v>
+        <v>7268207</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -2887,10 +2887,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121532890</v>
+        <v>121532473</v>
       </c>
       <c r="B23" t="n">
-        <v>78616</v>
+        <v>91014</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2903,21 +2903,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585516</v>
+        <v>585865</v>
       </c>
       <c r="R23" t="n">
-        <v>7268167</v>
+        <v>7268608</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3003,10 +3003,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121532473</v>
+        <v>121532890</v>
       </c>
       <c r="B24" t="n">
-        <v>91014</v>
+        <v>78616</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3019,21 +3019,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585865</v>
+        <v>585516</v>
       </c>
       <c r="R24" t="n">
-        <v>7268608</v>
+        <v>7268167</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 31799-2020 artfynd.xlsx
+++ b/artfynd/A 31799-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121476801</v>
+        <v>121477102</v>
       </c>
       <c r="B2" t="n">
-        <v>90724</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585865</v>
+        <v>585517</v>
       </c>
       <c r="R2" t="n">
-        <v>7268520</v>
+        <v>7268168</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121476691</v>
+        <v>121476384</v>
       </c>
       <c r="B3" t="n">
-        <v>91083</v>
+        <v>90728</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121476799</v>
+        <v>121476645</v>
       </c>
       <c r="B4" t="n">
-        <v>90724</v>
+        <v>91014</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585517</v>
+        <v>585866</v>
       </c>
       <c r="R4" t="n">
-        <v>7268168</v>
+        <v>7268608</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121476857</v>
+        <v>121476691</v>
       </c>
       <c r="B5" t="n">
-        <v>90742</v>
+        <v>91083</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>1506</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585596</v>
+        <v>585866</v>
       </c>
       <c r="R5" t="n">
-        <v>7268207</v>
+        <v>7268608</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121476482</v>
+        <v>121476960</v>
       </c>
       <c r="B6" t="n">
-        <v>56569</v>
+        <v>90746</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585919</v>
+        <v>585838</v>
       </c>
       <c r="R6" t="n">
-        <v>7268414</v>
+        <v>7268532</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121476959</v>
+        <v>121476482</v>
       </c>
       <c r="B7" t="n">
-        <v>90746</v>
+        <v>56569</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585881</v>
+        <v>585919</v>
       </c>
       <c r="R7" t="n">
-        <v>7268466</v>
+        <v>7268414</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121476960</v>
+        <v>121477108</v>
       </c>
       <c r="B8" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585838</v>
+        <v>585846</v>
       </c>
       <c r="R8" t="n">
-        <v>7268532</v>
+        <v>7268570</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121477108</v>
+        <v>121476957</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585846</v>
+        <v>585911</v>
       </c>
       <c r="R9" t="n">
-        <v>7268570</v>
+        <v>7268305</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121476725</v>
+        <v>121477106</v>
       </c>
       <c r="B10" t="n">
-        <v>77957</v>
+        <v>78616</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>498</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121476957</v>
+        <v>121476959</v>
       </c>
       <c r="B11" t="n">
         <v>90746</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585911</v>
+        <v>585881</v>
       </c>
       <c r="R11" t="n">
-        <v>7268305</v>
+        <v>7268466</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121476384</v>
+        <v>121476802</v>
       </c>
       <c r="B12" t="n">
-        <v>90728</v>
+        <v>90724</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585866</v>
+        <v>585846</v>
       </c>
       <c r="R12" t="n">
-        <v>7268608</v>
+        <v>7268570</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121476645</v>
+        <v>121476801</v>
       </c>
       <c r="B13" t="n">
-        <v>91014</v>
+        <v>90724</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585866</v>
+        <v>585865</v>
       </c>
       <c r="R13" t="n">
-        <v>7268608</v>
+        <v>7268520</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121477102</v>
+        <v>121476725</v>
       </c>
       <c r="B14" t="n">
-        <v>78616</v>
+        <v>77957</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585517</v>
+        <v>585865</v>
       </c>
       <c r="R14" t="n">
-        <v>7268168</v>
+        <v>7268520</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121477106</v>
+        <v>121476799</v>
       </c>
       <c r="B15" t="n">
-        <v>78616</v>
+        <v>90724</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585865</v>
+        <v>585517</v>
       </c>
       <c r="R15" t="n">
-        <v>7268520</v>
+        <v>7268168</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121476802</v>
+        <v>121476857</v>
       </c>
       <c r="B17" t="n">
-        <v>90724</v>
+        <v>90742</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585846</v>
+        <v>585596</v>
       </c>
       <c r="R17" t="n">
-        <v>7268570</v>
+        <v>7268207</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121532896</v>
+        <v>121532738</v>
       </c>
       <c r="B18" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585845</v>
+        <v>585826</v>
       </c>
       <c r="R18" t="n">
-        <v>7268570</v>
+        <v>7268200</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2423,7 +2423,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121532894</v>
+        <v>121532890</v>
       </c>
       <c r="B19" t="n">
         <v>78616</v>
@@ -2467,10 +2467,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585864</v>
+        <v>585516</v>
       </c>
       <c r="R19" t="n">
-        <v>7268519</v>
+        <v>7268167</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2539,10 +2539,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121532260</v>
+        <v>121532585</v>
       </c>
       <c r="B20" t="n">
-        <v>90728</v>
+        <v>90724</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2555,21 +2555,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585865</v>
+        <v>585516</v>
       </c>
       <c r="R20" t="n">
-        <v>7268608</v>
+        <v>7268167</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2655,10 +2655,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121532739</v>
+        <v>121532149</v>
       </c>
       <c r="B21" t="n">
-        <v>90746</v>
+        <v>91083</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2667,25 +2667,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>1506</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585910</v>
+        <v>585865</v>
       </c>
       <c r="R21" t="n">
-        <v>7268305</v>
+        <v>7268608</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2771,10 +2771,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121532738</v>
+        <v>121532473</v>
       </c>
       <c r="B22" t="n">
-        <v>90746</v>
+        <v>91014</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2787,21 +2787,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2815,10 +2815,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585826</v>
+        <v>585865</v>
       </c>
       <c r="R22" t="n">
-        <v>7268200</v>
+        <v>7268608</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2887,10 +2887,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121532473</v>
+        <v>121532260</v>
       </c>
       <c r="B23" t="n">
-        <v>91014</v>
+        <v>90728</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2903,21 +2903,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3003,10 +3003,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121532890</v>
+        <v>121532743</v>
       </c>
       <c r="B24" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3019,21 +3019,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585516</v>
+        <v>585837</v>
       </c>
       <c r="R24" t="n">
-        <v>7268167</v>
+        <v>7268531</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3119,10 +3119,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121532165</v>
+        <v>121532741</v>
       </c>
       <c r="B25" t="n">
-        <v>77957</v>
+        <v>90746</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3131,25 +3131,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>498</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585864</v>
+        <v>585880</v>
       </c>
       <c r="R25" t="n">
-        <v>7268519</v>
+        <v>7268465</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3235,10 +3235,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121532585</v>
+        <v>121532739</v>
       </c>
       <c r="B26" t="n">
-        <v>90724</v>
+        <v>90746</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3251,21 +3251,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585516</v>
+        <v>585910</v>
       </c>
       <c r="R26" t="n">
-        <v>7268167</v>
+        <v>7268305</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3351,10 +3351,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121532741</v>
+        <v>121532894</v>
       </c>
       <c r="B27" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3367,21 +3367,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3395,10 +3395,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585880</v>
+        <v>585864</v>
       </c>
       <c r="R27" t="n">
-        <v>7268465</v>
+        <v>7268519</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3467,10 +3467,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121532743</v>
+        <v>121532896</v>
       </c>
       <c r="B28" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3483,21 +3483,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585837</v>
+        <v>585845</v>
       </c>
       <c r="R28" t="n">
-        <v>7268531</v>
+        <v>7268570</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3583,10 +3583,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121532642</v>
+        <v>121532588</v>
       </c>
       <c r="B29" t="n">
-        <v>90742</v>
+        <v>90724</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3599,21 +3599,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585595</v>
+        <v>585845</v>
       </c>
       <c r="R29" t="n">
-        <v>7268207</v>
+        <v>7268570</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3699,10 +3699,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121532588</v>
+        <v>121532165</v>
       </c>
       <c r="B30" t="n">
-        <v>90724</v>
+        <v>77957</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3711,25 +3711,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3743,10 +3743,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585845</v>
+        <v>585864</v>
       </c>
       <c r="R30" t="n">
-        <v>7268570</v>
+        <v>7268519</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3931,10 +3931,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121532149</v>
+        <v>121532642</v>
       </c>
       <c r="B32" t="n">
-        <v>91083</v>
+        <v>90742</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3943,25 +3943,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1506</v>
+        <v>1204</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585865</v>
+        <v>585595</v>
       </c>
       <c r="R32" t="n">
-        <v>7268608</v>
+        <v>7268207</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
